--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-observation.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5674" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5674" uniqueCount="485">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -791,6 +791,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -7176,7 +7180,7 @@
         <v>74</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>74</v>
+        <v>253</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>74</v>
@@ -7184,10 +7188,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7213,10 +7217,10 @@
         <v>91</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7247,7 +7251,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>74</v>
@@ -7265,7 +7269,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7285,10 +7289,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7311,13 +7315,13 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7368,7 +7372,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7388,10 +7392,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7414,7 +7418,7 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -7447,7 +7451,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -7465,7 +7469,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7485,10 +7489,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7511,7 +7515,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -7564,7 +7568,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7584,10 +7588,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7643,25 +7647,25 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7681,10 +7685,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7760,7 +7764,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7780,10 +7784,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7881,10 +7885,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7984,10 +7988,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8087,10 +8091,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8190,10 +8194,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8293,10 +8297,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8396,10 +8400,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8497,10 +8501,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8598,10 +8602,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8701,10 +8705,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8802,10 +8806,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8903,10 +8907,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9006,10 +9010,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9107,10 +9111,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9210,10 +9214,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9311,10 +9315,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9408,10 +9412,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9513,10 +9517,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9616,10 +9620,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9711,7 +9715,7 @@
         <v>74</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>74</v>
+        <v>253</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>74</v>
@@ -9719,10 +9723,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9822,10 +9826,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9925,10 +9929,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9951,13 +9955,13 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9988,7 +9992,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>74</v>
@@ -10006,7 +10010,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -10026,10 +10030,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10052,13 +10056,13 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10089,25 +10093,25 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF81" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -10127,10 +10131,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10156,10 +10160,10 @@
         <v>161</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10210,7 +10214,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -10230,10 +10234,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10331,10 +10335,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10434,10 +10438,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10537,10 +10541,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10640,10 +10644,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10743,10 +10747,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10846,10 +10850,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10947,10 +10951,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11048,10 +11052,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11151,10 +11155,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11182,10 +11186,10 @@
         <v>200</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -11256,10 +11260,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11357,17 +11361,17 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F94" t="s" s="2">
         <v>80</v>
@@ -11385,11 +11389,11 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -11440,7 +11444,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11460,10 +11464,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11488,11 +11492,11 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11543,7 +11547,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11563,10 +11567,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11664,10 +11668,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11708,7 +11712,7 @@
         <v>74</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>74</v>
@@ -11767,10 +11771,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11811,7 +11815,7 @@
         <v>74</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>74</v>
@@ -11870,10 +11874,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11914,7 +11918,7 @@
         <v>74</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>74</v>
@@ -11973,10 +11977,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12076,10 +12080,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12120,7 +12124,7 @@
         <v>74</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>74</v>
@@ -12179,10 +12183,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12280,10 +12284,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12381,10 +12385,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12484,10 +12488,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12587,10 +12591,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12690,10 +12694,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12721,10 +12725,10 @@
         <v>161</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12755,7 +12759,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>74</v>
@@ -12773,7 +12777,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12793,10 +12797,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12896,10 +12900,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12922,7 +12926,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12975,7 +12979,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12995,10 +12999,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13021,7 +13025,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -13074,7 +13078,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -13094,10 +13098,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13120,7 +13124,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -13173,7 +13177,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -13193,10 +13197,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13219,7 +13223,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -13272,7 +13276,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -13292,10 +13296,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13318,7 +13322,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13371,7 +13375,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13391,10 +13395,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13417,7 +13421,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13470,7 +13474,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13490,10 +13494,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13516,7 +13520,7 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13557,7 +13561,7 @@
         <v>74</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AC115" s="2"/>
       <c r="AD115" t="s" s="2">
@@ -13567,7 +13571,7 @@
         <v>124</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13587,13 +13591,13 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>74</v>
@@ -13615,7 +13619,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13668,7 +13672,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13688,10 +13692,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13789,10 +13793,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13890,10 +13894,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13991,10 +13995,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14092,10 +14096,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14195,10 +14199,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14298,10 +14302,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14401,10 +14405,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14504,10 +14508,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14605,10 +14609,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14645,7 +14649,7 @@
         <v>74</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>74</v>
@@ -14664,7 +14668,7 @@
       </c>
       <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>74</v>
@@ -14682,7 +14686,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>75</v>
@@ -14702,10 +14706,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14732,7 +14736,7 @@
       </c>
       <c r="L127" s="2"/>
       <c r="M127" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -14783,7 +14787,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14803,10 +14807,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14833,7 +14837,7 @@
       </c>
       <c r="L128" s="2"/>
       <c r="M128" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -14884,7 +14888,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14904,10 +14908,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14983,7 +14987,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -15003,10 +15007,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15029,7 +15033,7 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -15082,7 +15086,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -15102,10 +15106,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15128,7 +15132,7 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
@@ -15181,7 +15185,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -15201,10 +15205,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15227,7 +15231,7 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -15280,7 +15284,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -15300,10 +15304,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15326,7 +15330,7 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -15379,7 +15383,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15399,10 +15403,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15425,7 +15429,7 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -15478,7 +15482,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15498,10 +15502,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15524,7 +15528,7 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -15577,7 +15581,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -15597,10 +15601,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15623,7 +15627,7 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -15676,7 +15680,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -15696,10 +15700,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15722,7 +15726,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -15775,7 +15779,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15795,10 +15799,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15821,7 +15825,7 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -15874,7 +15878,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -15894,10 +15898,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15920,7 +15924,7 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -15973,7 +15977,7 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -15993,10 +15997,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16019,7 +16023,7 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -16072,7 +16076,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -16092,13 +16096,13 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>74</v>
@@ -16120,7 +16124,7 @@
         <v>74</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
@@ -16173,7 +16177,7 @@
         <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -16193,10 +16197,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16294,10 +16298,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16395,10 +16399,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16496,10 +16500,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16597,10 +16601,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16700,10 +16704,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16803,10 +16807,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16906,10 +16910,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17009,10 +17013,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17110,10 +17114,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17150,7 +17154,7 @@
         <v>74</v>
       </c>
       <c r="S151" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T151" t="s" s="2">
         <v>74</v>
@@ -17169,7 +17173,7 @@
       </c>
       <c r="Y151" s="2"/>
       <c r="Z151" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>74</v>
@@ -17187,7 +17191,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>75</v>
@@ -17207,10 +17211,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17237,7 +17241,7 @@
       </c>
       <c r="L152" s="2"/>
       <c r="M152" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -17288,7 +17292,7 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -17308,10 +17312,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17338,7 +17342,7 @@
       </c>
       <c r="L153" s="2"/>
       <c r="M153" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -17389,7 +17393,7 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -17409,10 +17413,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17488,7 +17492,7 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -17508,10 +17512,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17534,7 +17538,7 @@
         <v>74</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -17587,7 +17591,7 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -17607,10 +17611,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17633,7 +17637,7 @@
         <v>74</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
@@ -17686,7 +17690,7 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -17706,10 +17710,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17732,7 +17736,7 @@
         <v>74</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
@@ -17785,7 +17789,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -17805,10 +17809,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17831,7 +17835,7 @@
         <v>74</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
@@ -17884,7 +17888,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -17904,10 +17908,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17930,7 +17934,7 @@
         <v>74</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
@@ -17983,7 +17987,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -18003,10 +18007,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18029,7 +18033,7 @@
         <v>74</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
@@ -18082,7 +18086,7 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -18102,10 +18106,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18128,7 +18132,7 @@
         <v>74</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
@@ -18181,7 +18185,7 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -18201,10 +18205,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18227,7 +18231,7 @@
         <v>74</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
@@ -18280,7 +18284,7 @@
         <v>74</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -18300,10 +18304,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18326,7 +18330,7 @@
         <v>74</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
@@ -18379,7 +18383,7 @@
         <v>74</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -18399,10 +18403,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18425,7 +18429,7 @@
         <v>74</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
@@ -18478,7 +18482,7 @@
         <v>74</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -18498,10 +18502,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18524,7 +18528,7 @@
         <v>74</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
@@ -18577,7 +18581,7 @@
         <v>74</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -18597,10 +18601,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18623,7 +18627,7 @@
         <v>74</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
@@ -18676,7 +18680,7 @@
         <v>74</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -18696,10 +18700,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18722,7 +18726,7 @@
         <v>74</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
@@ -18775,7 +18779,7 @@
         <v>74</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -18795,10 +18799,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18821,7 +18825,7 @@
         <v>74</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
@@ -18874,7 +18878,7 @@
         <v>74</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -18894,10 +18898,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -18920,11 +18924,11 @@
         <v>74</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L169" s="2"/>
       <c r="M169" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -18975,7 +18979,7 @@
         <v>74</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -18995,10 +18999,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19096,10 +19100,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19197,10 +19201,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19298,10 +19302,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19399,10 +19403,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19502,10 +19506,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19605,10 +19609,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -19708,10 +19712,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -19811,10 +19815,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -19912,10 +19916,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -19949,7 +19953,7 @@
       </c>
       <c r="Q179" s="2"/>
       <c r="R179" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="S179" t="s" s="2">
         <v>74</v>
@@ -19971,7 +19975,7 @@
       </c>
       <c r="Y179" s="2"/>
       <c r="Z179" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>74</v>
@@ -19989,7 +19993,7 @@
         <v>74</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -20009,10 +20013,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20035,7 +20039,7 @@
         <v>74</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L180" s="2"/>
       <c r="M180" s="2"/>
@@ -20088,7 +20092,7 @@
         <v>74</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>75</v>
@@ -20108,10 +20112,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20134,7 +20138,7 @@
         <v>74</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L181" s="2"/>
       <c r="M181" s="2"/>
@@ -20187,7 +20191,7 @@
         <v>74</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
